--- a/artfynd/A 62547-2019 artfynd.xlsx
+++ b/artfynd/A 62547-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121427064</v>
+        <v>121427062</v>
       </c>
       <c r="B2" t="n">
-        <v>90715</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515032</v>
+        <v>515019</v>
       </c>
       <c r="R2" t="n">
-        <v>6932862</v>
+        <v>6932897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121427062</v>
+        <v>121427064</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515019</v>
+        <v>515032</v>
       </c>
       <c r="R3" t="n">
-        <v>6932897</v>
+        <v>6932862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 62547-2019 artfynd.xlsx
+++ b/artfynd/A 62547-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121427062</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121427064</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 62547-2019 artfynd.xlsx
+++ b/artfynd/A 62547-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121427062</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121427064</v>
       </c>
       <c r="B3" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 62547-2019 artfynd.xlsx
+++ b/artfynd/A 62547-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121427062</v>
+        <v>121427064</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515019</v>
+        <v>515032</v>
       </c>
       <c r="R2" t="n">
-        <v>6932897</v>
+        <v>6932862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121427064</v>
+        <v>121427062</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515032</v>
+        <v>515019</v>
       </c>
       <c r="R3" t="n">
-        <v>6932862</v>
+        <v>6932897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 62547-2019 artfynd.xlsx
+++ b/artfynd/A 62547-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121427064</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121427062</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 62547-2019 artfynd.xlsx
+++ b/artfynd/A 62547-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121427064</v>
+        <v>121427062</v>
       </c>
       <c r="B2" t="n">
-        <v>90737</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515032</v>
+        <v>515019</v>
       </c>
       <c r="R2" t="n">
-        <v>6932862</v>
+        <v>6932897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121427062</v>
+        <v>121427064</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515019</v>
+        <v>515032</v>
       </c>
       <c r="R3" t="n">
-        <v>6932897</v>
+        <v>6932862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 62547-2019 artfynd.xlsx
+++ b/artfynd/A 62547-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121427062</v>
+        <v>121427064</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515019</v>
+        <v>515032</v>
       </c>
       <c r="R2" t="n">
-        <v>6932897</v>
+        <v>6932862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121427064</v>
+        <v>121427062</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515032</v>
+        <v>515019</v>
       </c>
       <c r="R3" t="n">
-        <v>6932862</v>
+        <v>6932897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 62547-2019 artfynd.xlsx
+++ b/artfynd/A 62547-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121427064</v>
+        <v>121427062</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515032</v>
+        <v>515019</v>
       </c>
       <c r="R2" t="n">
-        <v>6932862</v>
+        <v>6932897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121427062</v>
+        <v>121427064</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515019</v>
+        <v>515032</v>
       </c>
       <c r="R3" t="n">
-        <v>6932897</v>
+        <v>6932862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 62547-2019 artfynd.xlsx
+++ b/artfynd/A 62547-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121427064</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121427062</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 62547-2019 artfynd.xlsx
+++ b/artfynd/A 62547-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121427062</v>
+        <v>121427064</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515019</v>
+        <v>515032</v>
       </c>
       <c r="R2" t="n">
-        <v>6932897</v>
+        <v>6932862</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121427064</v>
+        <v>121427062</v>
       </c>
       <c r="B3" t="n">
-        <v>90746</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515032</v>
+        <v>515019</v>
       </c>
       <c r="R3" t="n">
-        <v>6932862</v>
+        <v>6932897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
